--- a/src/config/team_info.xlsx
+++ b/src/config/team_info.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xytron\Desktop\관제시스템-아빠와준형\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xytron\Desktop\RaceManager\latest_codes\race-gui\src\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8D18A5-A41F-445A-90F7-ECFD09E1E992}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F3F653-53B9-40EC-B91E-5652D9588202}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="29070" windowHeight="11220" xr2:uid="{EAE2933E-B873-4336-9604-E9E0C722E601}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="191">
   <si>
     <t>이름2</t>
   </si>
@@ -595,6 +595,14 @@
   </si>
   <si>
     <t>학교</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기권</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기권</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1020,143 +1028,146 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD631B50-24D0-4D05-81A3-3044F2FA1AB5}">
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="6" customWidth="1"/>
-    <col min="2" max="2" width="16.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.25" style="4" customWidth="1"/>
-    <col min="4" max="4" width="6.75" style="8" customWidth="1"/>
-    <col min="5" max="5" width="7.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" style="1" customWidth="1"/>
-    <col min="7" max="24" width="7.625" style="1" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="6.75" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="6.75" style="8" customWidth="1"/>
+    <col min="6" max="6" width="7.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.875" style="1" customWidth="1"/>
+    <col min="8" max="25" width="7.625" style="1" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="9">
+      <c r="E2" s="9">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
@@ -1164,337 +1175,344 @@
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="9">
+      <c r="E3" s="9">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="U3" s="2"/>
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="9">
+      <c r="E4" s="9">
         <v>4</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="Q4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="9">
+      <c r="E5" s="9">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="Q5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="U5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="W5" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="X5" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="X5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="9">
+      <c r="E6" s="9">
         <v>5</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="U6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="V6" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="X6" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="X6" s="2" t="s">
+      <c r="Y6" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D7" s="9">
+      <c r="E7" s="9">
         <v>3</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
@@ -1502,691 +1520,701 @@
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D8" s="9">
+      <c r="E8" s="9">
         <v>5</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="X8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="X8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D9" s="9">
+      <c r="E9" s="9">
         <v>4</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="I9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="U9" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D10" s="9">
+      <c r="E10" s="9">
         <v>4</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="S10" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="U10" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D11" s="9">
+      <c r="E11" s="9">
         <v>4</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="I11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="S11" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="T11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="U11" s="2"/>
+      <c r="U11" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5"/>
+      <c r="C12" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D12" s="9">
+      <c r="E12" s="9">
         <v>5</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="P12" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="Q12" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="S12" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="S12" s="2" t="s">
+      <c r="T12" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="T12" s="2" t="s">
+      <c r="U12" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="W12" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="X12" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="X12" s="2" t="s">
+      <c r="Y12" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="5"/>
+      <c r="C13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="9">
+      <c r="E13" s="9">
         <v>5</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="Q13" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="R13" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="S13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="T13" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="U13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="V13" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="V13" s="2" t="s">
+      <c r="W13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="W13" s="2" t="s">
+      <c r="X13" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="X13" s="2" t="s">
+      <c r="Y13" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="9">
+      <c r="E14" s="9">
         <v>5</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="I14" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M14" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="P14" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="S14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="T14" s="2" t="s">
+      <c r="U14" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="U14" s="2" t="s">
+      <c r="V14" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="V14" s="2" t="s">
+      <c r="W14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="W14" s="2" t="s">
+      <c r="X14" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="X14" s="2" t="s">
+      <c r="Y14" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D15" s="9">
+      <c r="E15" s="9">
         <v>5</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="I15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="P15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="Q15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="R15" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="R15" s="2" t="s">
+      <c r="S15" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="S15" s="2" t="s">
+      <c r="T15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="T15" s="2" t="s">
+      <c r="U15" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="U15" s="2" t="s">
+      <c r="V15" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="V15" s="2" t="s">
+      <c r="W15" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="W15" s="2" t="s">
+      <c r="X15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="X15" s="2" t="s">
+      <c r="Y15" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="9">
+      <c r="E16" s="9">
         <v>4</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="P16" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="R16" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="S16" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="T16" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="T16" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="U16" s="2"/>
+      <c r="U16" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
     </row>
-    <row r="17" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D17" s="9">
+      <c r="E17" s="9">
         <v>3</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="L17" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="M17" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="P17" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="P17" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q17" s="2"/>
+      <c r="Q17" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
@@ -2194,197 +2222,200 @@
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
     </row>
-    <row r="18" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="9">
+      <c r="E18" s="9">
         <v>5</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="I18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="P18" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="P18" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="Q18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="R18" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="R18" s="2" t="s">
+      <c r="S18" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="T18" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="U18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="V18" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="V18" s="2" t="s">
+      <c r="W18" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="W18" s="2" t="s">
+      <c r="X18" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="X18" s="2" t="s">
+      <c r="Y18" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D19" s="9">
+      <c r="E19" s="9">
         <v>4</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="I19" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="P19" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="Q19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="R19" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="R19" s="2" t="s">
+      <c r="S19" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="S19" s="2" t="s">
+      <c r="T19" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="T19" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="U19" s="2"/>
+      <c r="U19" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
     </row>
-    <row r="20" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="5"/>
+      <c r="C20" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D20" s="9">
+      <c r="E20" s="9">
         <v>3</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="I20" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="O20" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="P20" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="P20" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q20" s="2"/>
+      <c r="Q20" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
@@ -2392,231 +2423,237 @@
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
     </row>
-    <row r="21" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="5"/>
+      <c r="C21" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D21" s="9">
+      <c r="E21" s="9">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N21" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="P21" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="Q21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="R21" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="R21" s="2" t="s">
+      <c r="S21" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="S21" s="2" t="s">
+      <c r="T21" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="T21" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="U21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="V21" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="V21" s="2" t="s">
+      <c r="W21" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="W21" s="2" t="s">
+      <c r="X21" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="X21" s="2" t="s">
+      <c r="Y21" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D22" s="9">
+      <c r="E22" s="9">
         <v>5</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="L22" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="M22" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="P22" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="Q22" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="R22" s="2" t="s">
+      <c r="S22" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="S22" s="2" t="s">
+      <c r="T22" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="T22" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="U22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="V22" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="V22" s="2" t="s">
+      <c r="W22" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="W22" s="2" t="s">
+      <c r="X22" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="X22" s="2" t="s">
+      <c r="Y22" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="5"/>
+      <c r="C23" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D23" s="9">
+      <c r="E23" s="9">
         <v>5</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="I23" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="L23" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="L23" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="M23" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N23" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="O23" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="P23" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="Q23" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="R23" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="R23" s="2" t="s">
+      <c r="S23" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="S23" s="2" t="s">
+      <c r="T23" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="T23" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="U23" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="V23" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="V23" s="2" t="s">
+      <c r="W23" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="W23" s="2" t="s">
+      <c r="X23" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="X23" s="2" t="s">
+      <c r="Y23" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="10"/>
+    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E24" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/src/config/team_info.xlsx
+++ b/src/config/team_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xytron\Desktop\RaceManager\latest_codes\race-gui\src\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F3F653-53B9-40EC-B91E-5652D9588202}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF8A46F-7A58-4720-A42B-5F6A45250BE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="29070" windowHeight="11220" xr2:uid="{EAE2933E-B873-4336-9604-E9E0C722E601}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="175">
   <si>
     <t>이름2</t>
   </si>
@@ -279,21 +279,6 @@
     <t>배시연</t>
   </si>
   <si>
-    <t>마리오카트</t>
-  </si>
-  <si>
-    <t>최현홍</t>
-  </si>
-  <si>
-    <t>위서준</t>
-  </si>
-  <si>
-    <t>최정은</t>
-  </si>
-  <si>
-    <t>권나은</t>
-  </si>
-  <si>
     <t>비틀비틀</t>
   </si>
   <si>
@@ -363,21 +348,6 @@
     <t>박정환</t>
   </si>
   <si>
-    <t>토마스와 친구들</t>
-  </si>
-  <si>
-    <t>신윤환</t>
-  </si>
-  <si>
-    <t>김원빈</t>
-  </si>
-  <si>
-    <t>안은솔</t>
-  </si>
-  <si>
-    <t>김예인</t>
-  </si>
-  <si>
     <t>팀 카이</t>
   </si>
   <si>
@@ -504,15 +474,6 @@
     <t>강연우</t>
   </si>
   <si>
-    <t>자동차공학과</t>
-  </si>
-  <si>
-    <t>전자공학부 지능형ict융합전공</t>
-  </si>
-  <si>
-    <t>미래모빌리티학과</t>
-  </si>
-  <si>
     <t>경북대학교</t>
   </si>
   <si>
@@ -565,12 +526,6 @@
   </si>
   <si>
     <t>신준서</t>
-  </si>
-  <si>
-    <t>이준우</t>
-  </si>
-  <si>
-    <t>미래모빌리티공학과</t>
   </si>
   <si>
     <t>전기전자공학과</t>
@@ -590,10 +545,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Team SVE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>학교</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -602,7 +553,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>기권</t>
+    <t>TEAM SVE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1028,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD631B50-24D0-4D05-81A3-3044F2FA1AB5}">
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="6.75" style="6" customWidth="1"/>
@@ -1043,31 +994,31 @@
   <sheetData>
     <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>0</v>
@@ -1124,58 +1075,74 @@
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="E2" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
@@ -1183,66 +1150,74 @@
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>170</v>
       </c>
       <c r="E3" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>131</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>131</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>131</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
@@ -1250,61 +1225,61 @@
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" s="9">
         <v>4</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="M4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="P4" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
@@ -1317,73 +1292,73 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E5" s="9">
         <v>5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1392,126 +1367,124 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>185</v>
+        <v>128</v>
       </c>
       <c r="E6" s="9">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>190</v>
-      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="2" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="E7" s="9">
         <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
@@ -1528,73 +1501,73 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="2" t="s">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E8" s="9">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1603,61 +1576,61 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="E9" s="9">
         <v>4</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
@@ -1670,66 +1643,74 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E10" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="11" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
@@ -1737,66 +1718,74 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="2" t="s">
-        <v>186</v>
+        <v>107</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E11" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="12" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
@@ -1804,73 +1793,73 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="2" t="s">
-        <v>187</v>
+        <v>68</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="E12" s="9">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1879,73 +1868,73 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="2" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="E13" s="9">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="I13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="V13" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="W13" s="2" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1954,74 +1943,58 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="E14" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
     </row>
     <row r="15" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
@@ -2029,74 +2002,66 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="2" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="E15" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y15" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
     </row>
     <row r="16" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
@@ -2104,61 +2069,61 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E16" s="9">
         <v>4</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>143</v>
+        <v>22</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
@@ -2171,49 +2136,49 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="2" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="E17" s="9">
         <v>3</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="M17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O17" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="N17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="P17" s="2" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
@@ -2230,74 +2195,58 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="E18" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y18" s="2" t="s">
-        <v>137</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
     </row>
     <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
@@ -2305,66 +2254,74 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="2" t="s">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="E19" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>22</v>
+        <v>142</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
@@ -2372,54 +2329,62 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="2" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="E20" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
@@ -2431,229 +2396,69 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="2" t="s">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>177</v>
+        <v>133</v>
       </c>
       <c r="E21" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>177</v>
+        <v>133</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="I21" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="L21" s="2" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>177</v>
+        <v>133</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>177</v>
+        <v>133</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="X21" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="Y21" s="2" t="s">
-        <v>132</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
     </row>
     <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E22" s="9">
-        <v>5</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="X22" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y22" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E23" s="9">
-        <v>5</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="W23" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="X23" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y23" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E24" s="10"/>
+      <c r="E22" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
